--- a/examples/p18-synthetic-output-pack/renders/final/reopened/synthetic-cash-timing-model.xlsx
+++ b/examples/p18-synthetic-output-pack/renders/final/reopened/synthetic-cash-timing-model.xlsx
@@ -634,11 +634,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="62732818"/>
-        <c:axId val="87555527"/>
+        <c:axId val="6642185"/>
+        <c:axId val="74349442"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="62732818"/>
+        <c:axId val="6642185"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -704,7 +704,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87555527"/>
+        <c:crossAx val="74349442"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -712,7 +712,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="87555527"/>
+        <c:axId val="74349442"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="50"/>
@@ -790,7 +790,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62732818"/>
+        <c:crossAx val="6642185"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
